--- a/dist/molds.xlsx
+++ b/dist/molds.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="7245" yWindow="3405" windowWidth="28800" windowHeight="15435" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Log" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="145621" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,14 +42,6 @@
       <color theme="1"/>
       <sz val="11"/>
       <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <strike val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -443,7 +435,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -455,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C343"/>
+  <dimension ref="A1:C346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.42578125" customWidth="1" min="1" max="1"/>
@@ -499,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
@@ -1363,7 +1355,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72"/>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PMC123</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="n">
+        <v>26</v>
+      </c>
+    </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -2534,7 +2538,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163"/>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>PML123</t>
+        </is>
+      </c>
+    </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
@@ -4861,6 +4871,45 @@
       </c>
       <c r="C343" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>PML6511</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>1</v>
+      </c>
+      <c r="C344" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>1</v>
+      </c>
+      <c r="C345" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>PML5411</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>2</v>
+      </c>
+      <c r="C346" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -4876,7 +4925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5087,7 +5136,6 @@
           <t>2025-09-26T21:07:24</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>REMOVE/DECR</t>
@@ -5104,8 +5152,353 @@
       <c r="F8" t="n">
         <v>10</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-09-26T21:47:38</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ADD_NEW</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PML6511</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>new box</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-09-26T21:50:50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ADD_NEW</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>new box</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-09-26T21:51:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ADD/INCR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-09-26T21:52:19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>REMOVE/DECR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-09-26T21:52:44</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>REMOVE/DECR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PML6511</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-09-26T21:52:49</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>REMOVE/DECR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PML6511</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-09-26T21:53:26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NORMALIZE_ALL</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1 items</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-09-26T22:05:44</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ADD_NEW</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PML5411</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>25</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>new box</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-09-26T22:06:31</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ADD/INCR</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PML5411</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-09-26T22:06:36</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ADD/INCR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PML5411</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-09-26T22:07:32</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>REMOVE/DECR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>126D754H03</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-09-26T22:08:01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>REMOVE/DECR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PML5411</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-09-26T22:08:32</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NORMALIZE_ALL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1 items</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
